--- a/MIP_RULE/results/random_worst_piece_details.xlsx
+++ b/MIP_RULE/results/random_worst_piece_details.xlsx
@@ -530,22 +530,22 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>6.15</v>
+        <v>1.5</v>
       </c>
       <c r="J2" t="n">
-        <v>6.15</v>
+        <v>1.5</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>12</v>
+        <v>7.35</v>
       </c>
       <c r="M2" t="n">
-        <v>13.84</v>
+        <v>9.190000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>12</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="3">
@@ -578,22 +578,22 @@
         <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>11.15</v>
+        <v>6.5</v>
       </c>
       <c r="J3" t="n">
-        <v>13.83999999999206</v>
+        <v>9.189999999992068</v>
       </c>
       <c r="K3" t="n">
-        <v>2.689999999992063</v>
+        <v>2.689999999992068</v>
       </c>
       <c r="L3" t="n">
-        <v>20.35</v>
+        <v>15.7</v>
       </c>
       <c r="M3" t="n">
-        <v>22.86999999999206</v>
+        <v>18.21999999999207</v>
       </c>
       <c r="N3" t="n">
-        <v>20.35</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="4">
@@ -626,22 +626,22 @@
         <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>17.7</v>
+        <v>13.05</v>
       </c>
       <c r="J4" t="n">
-        <v>17.7</v>
+        <v>13.05</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>24.21</v>
+        <v>19.56</v>
       </c>
       <c r="M4" t="n">
-        <v>26.73</v>
+        <v>22.08</v>
       </c>
       <c r="N4" t="n">
-        <v>24.21</v>
+        <v>19.56</v>
       </c>
     </row>
     <row r="5">
@@ -914,22 +914,22 @@
         <v>40</v>
       </c>
       <c r="I10" t="n">
-        <v>46.15</v>
+        <v>41.5</v>
       </c>
       <c r="J10" t="n">
-        <v>46.15</v>
+        <v>41.5</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>52.66</v>
+        <v>48.01</v>
       </c>
       <c r="M10" t="n">
-        <v>55.18</v>
+        <v>50.53</v>
       </c>
       <c r="N10" t="n">
-        <v>52.66</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="11">
@@ -962,22 +962,22 @@
         <v>45</v>
       </c>
       <c r="I11" t="n">
-        <v>54.25</v>
+        <v>49.6</v>
       </c>
       <c r="J11" t="n">
-        <v>54.25</v>
+        <v>49.6</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>60.56</v>
+        <v>55.91</v>
       </c>
       <c r="M11" t="n">
-        <v>62.88</v>
+        <v>58.23</v>
       </c>
       <c r="N11" t="n">
-        <v>60.56</v>
+        <v>55.91</v>
       </c>
     </row>
     <row r="12">
@@ -1058,22 +1058,22 @@
         <v>55</v>
       </c>
       <c r="I13" t="n">
-        <v>64.25</v>
+        <v>59.6</v>
       </c>
       <c r="J13" t="n">
-        <v>64.25</v>
+        <v>59.6</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>69.59</v>
+        <v>64.94</v>
       </c>
       <c r="M13" t="n">
-        <v>70.92</v>
+        <v>66.27</v>
       </c>
       <c r="N13" t="n">
-        <v>69.59</v>
+        <v>64.94</v>
       </c>
     </row>
     <row r="14">
@@ -1106,22 +1106,22 @@
         <v>60</v>
       </c>
       <c r="I14" t="n">
-        <v>69.25</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>70.91999999999425</v>
+        <v>66.26999999999424</v>
       </c>
       <c r="K14" t="n">
         <v>1.669999999994246</v>
       </c>
       <c r="L14" t="n">
-        <v>76.73999999999425</v>
+        <v>72.08999999999425</v>
       </c>
       <c r="M14" t="n">
-        <v>78.56999999999425</v>
+        <v>73.91999999999425</v>
       </c>
       <c r="N14" t="n">
-        <v>76.73999999999425</v>
+        <v>72.08999999999425</v>
       </c>
     </row>
     <row r="15">
@@ -1154,22 +1154,22 @@
         <v>65</v>
       </c>
       <c r="I15" t="n">
-        <v>72.7</v>
+        <v>68.05</v>
       </c>
       <c r="J15" t="n">
-        <v>72.7</v>
+        <v>68.05</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>78.52000000000001</v>
+        <v>73.87</v>
       </c>
       <c r="M15" t="n">
-        <v>80.34999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="N15" t="n">
-        <v>78.52000000000001</v>
+        <v>73.87</v>
       </c>
     </row>
     <row r="16">
@@ -1250,22 +1250,22 @@
         <v>75</v>
       </c>
       <c r="I17" t="n">
-        <v>84.25</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>84.25</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>90.76000000000001</v>
+        <v>86.11</v>
       </c>
       <c r="M17" t="n">
-        <v>93.28</v>
+        <v>88.63</v>
       </c>
       <c r="N17" t="n">
-        <v>90.76000000000001</v>
+        <v>86.11</v>
       </c>
     </row>
     <row r="18">
@@ -1298,22 +1298,22 @@
         <v>80</v>
       </c>
       <c r="I18" t="n">
-        <v>89.25</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>93.27999999999221</v>
+        <v>88.62999999999221</v>
       </c>
       <c r="K18" t="n">
         <v>4.029999999992214</v>
       </c>
       <c r="L18" t="n">
-        <v>99.78999999999222</v>
+        <v>95.13999999999221</v>
       </c>
       <c r="M18" t="n">
-        <v>102.3099999999922</v>
+        <v>97.65999999999221</v>
       </c>
       <c r="N18" t="n">
-        <v>99.78999999999222</v>
+        <v>95.13999999999221</v>
       </c>
     </row>
     <row r="19">
@@ -1394,22 +1394,22 @@
         <v>90</v>
       </c>
       <c r="I20" t="n">
-        <v>99.25</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>102.3099999999836</v>
+        <v>97.65999999998361</v>
       </c>
       <c r="K20" t="n">
         <v>3.059999999983617</v>
       </c>
       <c r="L20" t="n">
-        <v>108.1599999999836</v>
+        <v>103.5099999999836</v>
       </c>
       <c r="M20" t="n">
-        <v>110</v>
+        <v>105.35</v>
       </c>
       <c r="N20" t="n">
-        <v>108.1599999999836</v>
+        <v>103.5099999999836</v>
       </c>
     </row>
     <row r="21">
@@ -1538,22 +1538,22 @@
         <v>105</v>
       </c>
       <c r="I23" t="n">
-        <v>112.7</v>
+        <v>108.05</v>
       </c>
       <c r="J23" t="n">
-        <v>112.7</v>
+        <v>108.05</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>118.21</v>
+        <v>113.56</v>
       </c>
       <c r="M23" t="n">
-        <v>119.73</v>
+        <v>115.08</v>
       </c>
       <c r="N23" t="n">
-        <v>118.21</v>
+        <v>113.56</v>
       </c>
     </row>
     <row r="24">
@@ -1682,22 +1682,22 @@
         <v>120</v>
       </c>
       <c r="I26" t="n">
-        <v>129.25</v>
+        <v>124.6</v>
       </c>
       <c r="J26" t="n">
-        <v>129.25</v>
+        <v>124.6</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>135.07</v>
+        <v>130.42</v>
       </c>
       <c r="M26" t="n">
-        <v>136.9</v>
+        <v>132.25</v>
       </c>
       <c r="N26" t="n">
-        <v>135.07</v>
+        <v>130.42</v>
       </c>
     </row>
     <row r="27">
@@ -1874,22 +1874,22 @@
         <v>140</v>
       </c>
       <c r="I30" t="n">
-        <v>149.25</v>
+        <v>144.6</v>
       </c>
       <c r="J30" t="n">
-        <v>149.25</v>
+        <v>144.6</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>155.76</v>
+        <v>151.11</v>
       </c>
       <c r="M30" t="n">
-        <v>158.28</v>
+        <v>153.63</v>
       </c>
       <c r="N30" t="n">
-        <v>155.76</v>
+        <v>151.11</v>
       </c>
     </row>
     <row r="31">
@@ -2066,22 +2066,22 @@
         <v>160</v>
       </c>
       <c r="I34" t="n">
-        <v>167.7</v>
+        <v>163.05</v>
       </c>
       <c r="J34" t="n">
-        <v>167.7</v>
+        <v>163.05</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>174.01</v>
+        <v>169.36</v>
       </c>
       <c r="M34" t="n">
-        <v>176.33</v>
+        <v>171.68</v>
       </c>
       <c r="N34" t="n">
-        <v>182.6399999999948</v>
+        <v>177.9899999999948</v>
       </c>
     </row>
     <row r="35">
@@ -2114,22 +2114,22 @@
         <v>165</v>
       </c>
       <c r="I35" t="n">
-        <v>172.7</v>
+        <v>168.05</v>
       </c>
       <c r="J35" t="n">
-        <v>176.3299999999948</v>
+        <v>171.6799999999948</v>
       </c>
       <c r="K35" t="n">
         <v>3.629999999994766</v>
       </c>
       <c r="L35" t="n">
-        <v>182.6399999999948</v>
+        <v>177.9899999999948</v>
       </c>
       <c r="M35" t="n">
-        <v>184.9599999999947</v>
+        <v>180.3099999999948</v>
       </c>
       <c r="N35" t="n">
-        <v>182.6399999999948</v>
+        <v>177.9899999999948</v>
       </c>
     </row>
     <row r="36">
@@ -2258,22 +2258,22 @@
         <v>180</v>
       </c>
       <c r="I38" t="n">
-        <v>187.7</v>
+        <v>183.05</v>
       </c>
       <c r="J38" t="n">
-        <v>187.7</v>
+        <v>183.05</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>193.04</v>
+        <v>188.39</v>
       </c>
       <c r="M38" t="n">
-        <v>194.37</v>
+        <v>189.72</v>
       </c>
       <c r="N38" t="n">
-        <v>193.04</v>
+        <v>188.39</v>
       </c>
     </row>
     <row r="39">
@@ -2354,22 +2354,22 @@
         <v>190</v>
       </c>
       <c r="I40" t="n">
-        <v>196.15</v>
+        <v>191.5</v>
       </c>
       <c r="J40" t="n">
-        <v>196.15</v>
+        <v>191.5</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>201.97</v>
+        <v>197.32</v>
       </c>
       <c r="M40" t="n">
-        <v>203.8</v>
+        <v>199.15</v>
       </c>
       <c r="N40" t="n">
-        <v>201.97</v>
+        <v>197.32</v>
       </c>
     </row>
     <row r="41">
@@ -2450,22 +2450,22 @@
         <v>200</v>
       </c>
       <c r="I42" t="n">
-        <v>209.25</v>
+        <v>204.6</v>
       </c>
       <c r="J42" t="n">
-        <v>209.25</v>
+        <v>204.6</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>215.43</v>
+        <v>210.78</v>
       </c>
       <c r="M42" t="n">
-        <v>217.61</v>
+        <v>212.96</v>
       </c>
       <c r="N42" t="n">
-        <v>215.43</v>
+        <v>210.78</v>
       </c>
     </row>
     <row r="43">
@@ -2642,22 +2642,22 @@
         <v>220</v>
       </c>
       <c r="I46" t="n">
-        <v>226.15</v>
+        <v>221.5</v>
       </c>
       <c r="J46" t="n">
-        <v>226.15</v>
+        <v>221.5</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>231.66</v>
+        <v>227.01</v>
       </c>
       <c r="M46" t="n">
-        <v>233.18</v>
+        <v>228.53</v>
       </c>
       <c r="N46" t="n">
-        <v>231.66</v>
+        <v>227.01</v>
       </c>
     </row>
     <row r="47">
@@ -2738,22 +2738,22 @@
         <v>230</v>
       </c>
       <c r="I48" t="n">
-        <v>236.15</v>
+        <v>231.5</v>
       </c>
       <c r="J48" t="n">
-        <v>236.15</v>
+        <v>231.5</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>242</v>
+        <v>237.35</v>
       </c>
       <c r="M48" t="n">
-        <v>243.84</v>
+        <v>239.19</v>
       </c>
       <c r="N48" t="n">
-        <v>242</v>
+        <v>237.35</v>
       </c>
     </row>
     <row r="49">
@@ -2882,22 +2882,22 @@
         <v>245</v>
       </c>
       <c r="I51" t="n">
-        <v>252.7</v>
+        <v>248.05</v>
       </c>
       <c r="J51" t="n">
-        <v>252.7</v>
+        <v>248.05</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>259.21</v>
+        <v>254.56</v>
       </c>
       <c r="M51" t="n">
-        <v>261.73</v>
+        <v>257.08</v>
       </c>
       <c r="N51" t="n">
-        <v>259.21</v>
+        <v>254.56</v>
       </c>
     </row>
     <row r="52">
@@ -2930,22 +2930,22 @@
         <v>250</v>
       </c>
       <c r="I52" t="n">
-        <v>256.15</v>
+        <v>251.5</v>
       </c>
       <c r="J52" t="n">
-        <v>256.15</v>
+        <v>251.5</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>261.97</v>
+        <v>257.32</v>
       </c>
       <c r="M52" t="n">
-        <v>263.8</v>
+        <v>259.15</v>
       </c>
       <c r="N52" t="n">
-        <v>269.6199999999941</v>
+        <v>264.9699999999942</v>
       </c>
     </row>
     <row r="53">
@@ -2978,22 +2978,22 @@
         <v>255</v>
       </c>
       <c r="I53" t="n">
-        <v>261.15</v>
+        <v>256.5</v>
       </c>
       <c r="J53" t="n">
-        <v>263.8</v>
+        <v>259.15</v>
       </c>
       <c r="K53" t="n">
-        <v>2.65</v>
+        <v>2.649999999999977</v>
       </c>
       <c r="L53" t="n">
-        <v>269.6199999999941</v>
+        <v>264.9699999999942</v>
       </c>
       <c r="M53" t="n">
-        <v>271.45</v>
+        <v>266.8</v>
       </c>
       <c r="N53" t="n">
-        <v>269.6199999999941</v>
+        <v>264.9699999999942</v>
       </c>
     </row>
     <row r="54">
@@ -3170,22 +3170,22 @@
         <v>275</v>
       </c>
       <c r="I57" t="n">
-        <v>282.7</v>
+        <v>278.05</v>
       </c>
       <c r="J57" t="n">
-        <v>282.7</v>
+        <v>278.05</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>289.01</v>
+        <v>284.36</v>
       </c>
       <c r="M57" t="n">
-        <v>291.33</v>
+        <v>286.68</v>
       </c>
       <c r="N57" t="n">
-        <v>289.01</v>
+        <v>284.36</v>
       </c>
     </row>
     <row r="58">
@@ -3266,22 +3266,22 @@
         <v>285</v>
       </c>
       <c r="I59" t="n">
-        <v>292.7</v>
+        <v>288.05</v>
       </c>
       <c r="J59" t="n">
-        <v>292.7</v>
+        <v>288.05</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>298.55</v>
+        <v>293.9</v>
       </c>
       <c r="M59" t="n">
-        <v>300.39</v>
+        <v>295.74</v>
       </c>
       <c r="N59" t="n">
-        <v>298.55</v>
+        <v>293.9</v>
       </c>
     </row>
     <row r="60">
@@ -3410,22 +3410,22 @@
         <v>300</v>
       </c>
       <c r="I62" t="n">
-        <v>306.15</v>
+        <v>301.5</v>
       </c>
       <c r="J62" t="n">
-        <v>306.15</v>
+        <v>301.5</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>312.46</v>
+        <v>307.81</v>
       </c>
       <c r="M62" t="n">
-        <v>314.78</v>
+        <v>310.13</v>
       </c>
       <c r="N62" t="n">
-        <v>312.46</v>
+        <v>307.81</v>
       </c>
     </row>
     <row r="63">
@@ -3602,22 +3602,22 @@
         <v>320</v>
       </c>
       <c r="I66" t="n">
-        <v>327.7</v>
+        <v>323.05</v>
       </c>
       <c r="J66" t="n">
-        <v>327.7</v>
+        <v>323.05</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>333.52</v>
+        <v>328.87</v>
       </c>
       <c r="M66" t="n">
-        <v>335.35</v>
+        <v>330.7</v>
       </c>
       <c r="N66" t="n">
-        <v>333.52</v>
+        <v>328.87</v>
       </c>
     </row>
     <row r="67">
@@ -3650,22 +3650,22 @@
         <v>325</v>
       </c>
       <c r="I67" t="n">
-        <v>332.7</v>
+        <v>328.05</v>
       </c>
       <c r="J67" t="n">
-        <v>335.35</v>
+        <v>330.7</v>
       </c>
       <c r="K67" t="n">
-        <v>2.65</v>
+        <v>2.649999999999977</v>
       </c>
       <c r="L67" t="n">
-        <v>341.5299999999978</v>
+        <v>336.8799999999978</v>
       </c>
       <c r="M67" t="n">
-        <v>343.7099999999978</v>
+        <v>339.0599999999978</v>
       </c>
       <c r="N67" t="n">
-        <v>341.5299999999978</v>
+        <v>336.8799999999978</v>
       </c>
     </row>
     <row r="68">
@@ -3698,22 +3698,22 @@
         <v>330</v>
       </c>
       <c r="I68" t="n">
-        <v>337.7</v>
+        <v>333.05</v>
       </c>
       <c r="J68" t="n">
-        <v>343.7099999999947</v>
+        <v>339.0599999999948</v>
       </c>
       <c r="K68" t="n">
         <v>6.009999999994761</v>
       </c>
       <c r="L68" t="n">
-        <v>349.5599999999948</v>
+        <v>344.9099999999948</v>
       </c>
       <c r="M68" t="n">
-        <v>351.4</v>
+        <v>346.75</v>
       </c>
       <c r="N68" t="n">
-        <v>349.5599999999948</v>
+        <v>344.9099999999948</v>
       </c>
     </row>
     <row r="69">
@@ -3794,22 +3794,22 @@
         <v>340</v>
       </c>
       <c r="I70" t="n">
-        <v>347.7</v>
+        <v>343.05</v>
       </c>
       <c r="J70" t="n">
-        <v>351.4</v>
+        <v>346.75</v>
       </c>
       <c r="K70" t="n">
         <v>3.699999999999989</v>
       </c>
       <c r="L70" t="n">
-        <v>357.9099999999898</v>
+        <v>353.2599999999898</v>
       </c>
       <c r="M70" t="n">
-        <v>360.4299999999898</v>
+        <v>355.7799999999899</v>
       </c>
       <c r="N70" t="n">
-        <v>357.9099999999898</v>
+        <v>353.2599999999898</v>
       </c>
     </row>
     <row r="71">
@@ -3842,22 +3842,22 @@
         <v>345</v>
       </c>
       <c r="I71" t="n">
-        <v>351.15</v>
+        <v>346.5</v>
       </c>
       <c r="J71" t="n">
-        <v>351.15</v>
+        <v>346.5</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>357.46</v>
+        <v>352.81</v>
       </c>
       <c r="M71" t="n">
-        <v>359.78</v>
+        <v>355.13</v>
       </c>
       <c r="N71" t="n">
-        <v>357.46</v>
+        <v>352.81</v>
       </c>
     </row>
     <row r="72">
@@ -3986,22 +3986,22 @@
         <v>360</v>
       </c>
       <c r="I74" t="n">
-        <v>369.25</v>
+        <v>364.6</v>
       </c>
       <c r="J74" t="n">
-        <v>369.25</v>
+        <v>364.6</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>375.56</v>
+        <v>370.91</v>
       </c>
       <c r="M74" t="n">
-        <v>377.88</v>
+        <v>373.23</v>
       </c>
       <c r="N74" t="n">
-        <v>375.56</v>
+        <v>370.91</v>
       </c>
     </row>
     <row r="75">
@@ -4034,22 +4034,22 @@
         <v>365</v>
       </c>
       <c r="I75" t="n">
-        <v>374.25</v>
+        <v>369.6</v>
       </c>
       <c r="J75" t="n">
-        <v>377.8799999999974</v>
+        <v>373.2299999999974</v>
       </c>
       <c r="K75" t="n">
         <v>3.629999999997381</v>
       </c>
       <c r="L75" t="n">
-        <v>383.3899999999974</v>
+        <v>378.7399999999974</v>
       </c>
       <c r="M75" t="n">
-        <v>384.9099999999974</v>
+        <v>380.2599999999974</v>
       </c>
       <c r="N75" t="n">
-        <v>383.3899999999974</v>
+        <v>378.7399999999974</v>
       </c>
     </row>
     <row r="76">
@@ -4082,22 +4082,22 @@
         <v>370</v>
       </c>
       <c r="I76" t="n">
-        <v>377.7</v>
+        <v>373.05</v>
       </c>
       <c r="J76" t="n">
-        <v>377.7</v>
+        <v>373.05</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>384.01</v>
+        <v>379.36</v>
       </c>
       <c r="M76" t="n">
-        <v>386.33</v>
+        <v>381.68</v>
       </c>
       <c r="N76" t="n">
-        <v>384.01</v>
+        <v>379.36</v>
       </c>
     </row>
     <row r="77">
@@ -4130,22 +4130,22 @@
         <v>375</v>
       </c>
       <c r="I77" t="n">
-        <v>381.15</v>
+        <v>376.5</v>
       </c>
       <c r="J77" t="n">
-        <v>381.15</v>
+        <v>376.5</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>387.66</v>
+        <v>383.01</v>
       </c>
       <c r="M77" t="n">
-        <v>390.1799999999999</v>
+        <v>385.53</v>
       </c>
       <c r="N77" t="n">
-        <v>387.66</v>
+        <v>383.01</v>
       </c>
     </row>
     <row r="78">
@@ -4178,22 +4178,22 @@
         <v>380</v>
       </c>
       <c r="I78" t="n">
-        <v>386.15</v>
+        <v>381.5</v>
       </c>
       <c r="J78" t="n">
-        <v>390.1799999999952</v>
+        <v>385.5299999999952</v>
       </c>
       <c r="K78" t="n">
         <v>4.029999999995198</v>
       </c>
       <c r="L78" t="n">
-        <v>396.4899999999952</v>
+        <v>391.8399999999952</v>
       </c>
       <c r="M78" t="n">
-        <v>398.8099999999952</v>
+        <v>394.1599999999952</v>
       </c>
       <c r="N78" t="n">
-        <v>396.4899999999952</v>
+        <v>391.8399999999952</v>
       </c>
     </row>
     <row r="79">
@@ -4226,22 +4226,22 @@
         <v>385</v>
       </c>
       <c r="I79" t="n">
-        <v>391.15</v>
+        <v>386.5</v>
       </c>
       <c r="J79" t="n">
-        <v>398.8099999999926</v>
+        <v>394.1599999999926</v>
       </c>
       <c r="K79" t="n">
         <v>7.659999999992579</v>
       </c>
       <c r="L79" t="n">
-        <v>404.9899999999926</v>
+        <v>400.3399999999926</v>
       </c>
       <c r="M79" t="n">
-        <v>407.1699999999926</v>
+        <v>402.5199999999926</v>
       </c>
       <c r="N79" t="n">
-        <v>404.9899999999926</v>
+        <v>400.3399999999926</v>
       </c>
     </row>
     <row r="80">
@@ -4274,22 +4274,22 @@
         <v>390</v>
       </c>
       <c r="I80" t="n">
-        <v>396.15</v>
+        <v>391.5</v>
       </c>
       <c r="J80" t="n">
-        <v>407.1699999999895</v>
+        <v>402.5199999999895</v>
       </c>
       <c r="K80" t="n">
         <v>11.01999999998952</v>
       </c>
       <c r="L80" t="n">
-        <v>413.4799999999895</v>
+        <v>408.8299999999895</v>
       </c>
       <c r="M80" t="n">
-        <v>415.8</v>
+        <v>411.15</v>
       </c>
       <c r="N80" t="n">
-        <v>413.4799999999895</v>
+        <v>408.8299999999895</v>
       </c>
     </row>
     <row r="81">
@@ -4322,22 +4322,22 @@
         <v>395</v>
       </c>
       <c r="I81" t="n">
-        <v>404.25</v>
+        <v>399.6</v>
       </c>
       <c r="J81" t="n">
-        <v>404.25</v>
+        <v>399.6</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>410.56</v>
+        <v>405.91</v>
       </c>
       <c r="M81" t="n">
-        <v>412.88</v>
+        <v>408.23</v>
       </c>
       <c r="N81" t="n">
-        <v>410.56</v>
+        <v>405.91</v>
       </c>
     </row>
     <row r="82">
@@ -4370,22 +4370,22 @@
         <v>400</v>
       </c>
       <c r="I82" t="n">
-        <v>406.15</v>
+        <v>401.5</v>
       </c>
       <c r="J82" t="n">
-        <v>415.8</v>
+        <v>411.15</v>
       </c>
       <c r="K82" t="n">
-        <v>9.65</v>
+        <v>9.649999999999977</v>
       </c>
       <c r="L82" t="n">
-        <v>421.9799999999869</v>
+        <v>417.3299999999869</v>
       </c>
       <c r="M82" t="n">
-        <v>424.1599999999869</v>
+        <v>419.5099999999869</v>
       </c>
       <c r="N82" t="n">
-        <v>421.9799999999869</v>
+        <v>417.3299999999869</v>
       </c>
     </row>
     <row r="83">
@@ -4706,22 +4706,22 @@
         <v>435</v>
       </c>
       <c r="I89" t="n">
-        <v>442.7</v>
+        <v>438.05</v>
       </c>
       <c r="J89" t="n">
-        <v>442.7</v>
+        <v>438.05</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>448.88</v>
+        <v>444.23</v>
       </c>
       <c r="M89" t="n">
-        <v>451.06</v>
+        <v>446.41</v>
       </c>
       <c r="N89" t="n">
-        <v>448.88</v>
+        <v>444.23</v>
       </c>
     </row>
     <row r="90">
@@ -4754,22 +4754,22 @@
         <v>440</v>
       </c>
       <c r="I90" t="n">
-        <v>449.25</v>
+        <v>444.6</v>
       </c>
       <c r="J90" t="n">
-        <v>449.25</v>
+        <v>444.6</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>455.43</v>
+        <v>450.78</v>
       </c>
       <c r="M90" t="n">
-        <v>457.61</v>
+        <v>452.96</v>
       </c>
       <c r="N90" t="n">
-        <v>510.7799999999913</v>
+        <v>506.1299999999913</v>
       </c>
     </row>
     <row r="91">
@@ -4802,22 +4802,22 @@
         <v>445</v>
       </c>
       <c r="I91" t="n">
-        <v>454.25</v>
+        <v>449.6</v>
       </c>
       <c r="J91" t="n">
-        <v>457.6099999999969</v>
+        <v>452.959999999997</v>
       </c>
       <c r="K91" t="n">
         <v>3.359999999996944</v>
       </c>
       <c r="L91" t="n">
-        <v>463.9199999999969</v>
+        <v>459.269999999997</v>
       </c>
       <c r="M91" t="n">
-        <v>466.2399999999969</v>
+        <v>461.589999999997</v>
       </c>
       <c r="N91" t="n">
-        <v>519.2699999999882</v>
+        <v>514.6199999999882</v>
       </c>
     </row>
     <row r="92">
@@ -4850,22 +4850,22 @@
         <v>450</v>
       </c>
       <c r="I92" t="n">
-        <v>459.25</v>
+        <v>454.6</v>
       </c>
       <c r="J92" t="n">
-        <v>466.2399999999943</v>
+        <v>461.5899999999943</v>
       </c>
       <c r="K92" t="n">
         <v>6.989999999994325</v>
       </c>
       <c r="L92" t="n">
-        <v>472.0899999999943</v>
+        <v>467.4399999999944</v>
       </c>
       <c r="M92" t="n">
-        <v>473.9299999999943</v>
+        <v>469.2799999999943</v>
       </c>
       <c r="N92" t="n">
-        <v>535.1299999999807</v>
+        <v>530.4799999999807</v>
       </c>
     </row>
     <row r="93">
@@ -4946,22 +4946,22 @@
         <v>460</v>
       </c>
       <c r="I94" t="n">
-        <v>467.7</v>
+        <v>463.05</v>
       </c>
       <c r="J94" t="n">
-        <v>467.7</v>
+        <v>463.05</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>474.01</v>
+        <v>469.36</v>
       </c>
       <c r="M94" t="n">
-        <v>476.33</v>
+        <v>471.68</v>
       </c>
       <c r="N94" t="n">
-        <v>509.01</v>
+        <v>504.36</v>
       </c>
     </row>
     <row r="95">
@@ -4994,22 +4994,22 @@
         <v>465</v>
       </c>
       <c r="I95" t="n">
-        <v>471.15</v>
+        <v>466.5</v>
       </c>
       <c r="J95" t="n">
-        <v>471.15</v>
+        <v>466.5</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>476.49</v>
+        <v>471.84</v>
       </c>
       <c r="M95" t="n">
-        <v>477.82</v>
+        <v>473.17</v>
       </c>
       <c r="N95" t="n">
-        <v>511.49</v>
+        <v>506.84</v>
       </c>
     </row>
     <row r="96">
@@ -5042,22 +5042,22 @@
         <v>470</v>
       </c>
       <c r="I96" t="n">
-        <v>479.25</v>
+        <v>474.6</v>
       </c>
       <c r="J96" t="n">
-        <v>479.25</v>
+        <v>474.6</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>485.43</v>
+        <v>480.78</v>
       </c>
       <c r="M96" t="n">
-        <v>487.61</v>
+        <v>482.96</v>
       </c>
       <c r="N96" t="n">
-        <v>510.7799999999913</v>
+        <v>506.1299999999913</v>
       </c>
     </row>
     <row r="97">
@@ -5090,22 +5090,22 @@
         <v>475</v>
       </c>
       <c r="I97" t="n">
-        <v>484.25</v>
+        <v>479.6</v>
       </c>
       <c r="J97" t="n">
-        <v>487.6099999999969</v>
+        <v>482.959999999997</v>
       </c>
       <c r="K97" t="n">
         <v>3.359999999996944</v>
       </c>
       <c r="L97" t="n">
-        <v>493.9199999999969</v>
+        <v>489.269999999997</v>
       </c>
       <c r="M97" t="n">
-        <v>496.2399999999969</v>
+        <v>491.589999999997</v>
       </c>
       <c r="N97" t="n">
-        <v>519.2699999999882</v>
+        <v>514.6199999999882</v>
       </c>
     </row>
     <row r="98">
@@ -5138,22 +5138,22 @@
         <v>480</v>
       </c>
       <c r="I98" t="n">
-        <v>489.25</v>
+        <v>484.6</v>
       </c>
       <c r="J98" t="n">
-        <v>496.2399999999943</v>
+        <v>491.5899999999943</v>
       </c>
       <c r="K98" t="n">
         <v>6.989999999994325</v>
       </c>
       <c r="L98" t="n">
-        <v>502.4199999999943</v>
+        <v>497.7699999999944</v>
       </c>
       <c r="M98" t="n">
-        <v>504.6</v>
+        <v>499.95</v>
       </c>
       <c r="N98" t="n">
-        <v>510.7799999999913</v>
+        <v>506.1299999999913</v>
       </c>
     </row>
     <row r="99">
@@ -5186,22 +5186,22 @@
         <v>485</v>
       </c>
       <c r="I99" t="n">
-        <v>494.25</v>
+        <v>489.6</v>
       </c>
       <c r="J99" t="n">
-        <v>504.6</v>
+        <v>499.95</v>
       </c>
       <c r="K99" t="n">
-        <v>10.35</v>
+        <v>10.34999999999997</v>
       </c>
       <c r="L99" t="n">
-        <v>510.7799999999913</v>
+        <v>506.1299999999913</v>
       </c>
       <c r="M99" t="n">
-        <v>512.9599999999913</v>
+        <v>508.3099999999913</v>
       </c>
       <c r="N99" t="n">
-        <v>510.7799999999913</v>
+        <v>506.1299999999913</v>
       </c>
     </row>
     <row r="100">
@@ -5234,22 +5234,22 @@
         <v>490</v>
       </c>
       <c r="I100" t="n">
-        <v>499.25</v>
+        <v>494.6</v>
       </c>
       <c r="J100" t="n">
-        <v>512.9599999999882</v>
+        <v>508.3099999999882</v>
       </c>
       <c r="K100" t="n">
         <v>13.70999999998821</v>
       </c>
       <c r="L100" t="n">
-        <v>519.2699999999882</v>
+        <v>514.6199999999882</v>
       </c>
       <c r="M100" t="n">
-        <v>521.5899999999882</v>
+        <v>516.9399999999882</v>
       </c>
       <c r="N100" t="n">
-        <v>519.2699999999882</v>
+        <v>514.6199999999882</v>
       </c>
     </row>
     <row r="101">
@@ -5282,22 +5282,22 @@
         <v>495</v>
       </c>
       <c r="I101" t="n">
-        <v>502.7</v>
+        <v>498.05</v>
       </c>
       <c r="J101" t="n">
-        <v>502.7</v>
+        <v>498.05</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>509.01</v>
+        <v>504.36</v>
       </c>
       <c r="M101" t="n">
-        <v>511.33</v>
+        <v>506.68</v>
       </c>
       <c r="N101" t="n">
-        <v>509.01</v>
+        <v>504.36</v>
       </c>
     </row>
     <row r="102">
@@ -5330,22 +5330,22 @@
         <v>500</v>
       </c>
       <c r="I102" t="n">
-        <v>506.15</v>
+        <v>501.5</v>
       </c>
       <c r="J102" t="n">
-        <v>506.15</v>
+        <v>501.5</v>
       </c>
       <c r="K102" t="n">
         <v>0</v>
       </c>
       <c r="L102" t="n">
-        <v>511.49</v>
+        <v>506.84</v>
       </c>
       <c r="M102" t="n">
-        <v>512.8199999999999</v>
+        <v>508.17</v>
       </c>
       <c r="N102" t="n">
-        <v>511.49</v>
+        <v>506.84</v>
       </c>
     </row>
     <row r="103">
@@ -5378,22 +5378,22 @@
         <v>505</v>
       </c>
       <c r="I103" t="n">
-        <v>514.25</v>
+        <v>509.6</v>
       </c>
       <c r="J103" t="n">
-        <v>521.5899999999856</v>
+        <v>516.9399999999856</v>
       </c>
       <c r="K103" t="n">
         <v>7.339999999985594</v>
       </c>
       <c r="L103" t="n">
-        <v>527.4399999999856</v>
+        <v>522.7899999999856</v>
       </c>
       <c r="M103" t="n">
-        <v>529.2799999999856</v>
+        <v>524.6299999999857</v>
       </c>
       <c r="N103" t="n">
-        <v>535.1299999999807</v>
+        <v>530.4799999999807</v>
       </c>
     </row>
     <row r="104">
@@ -5426,22 +5426,22 @@
         <v>510</v>
       </c>
       <c r="I104" t="n">
-        <v>519.25</v>
+        <v>514.6</v>
       </c>
       <c r="J104" t="n">
-        <v>529.2799999999806</v>
+        <v>524.6299999999807</v>
       </c>
       <c r="K104" t="n">
         <v>10.02999999998065</v>
       </c>
       <c r="L104" t="n">
-        <v>535.1299999999807</v>
+        <v>530.4799999999807</v>
       </c>
       <c r="M104" t="n">
-        <v>536.9699999999807</v>
+        <v>532.3199999999807</v>
       </c>
       <c r="N104" t="n">
-        <v>535.1299999999807</v>
+        <v>530.4799999999807</v>
       </c>
     </row>
   </sheetData>

--- a/MIP_RULE/results/random_worst_piece_details.xlsx
+++ b/MIP_RULE/results/random_worst_piece_details.xlsx
@@ -2984,7 +2984,7 @@
         <v>259.15</v>
       </c>
       <c r="K53" t="n">
-        <v>2.649999999999977</v>
+        <v>2.65</v>
       </c>
       <c r="L53" t="n">
         <v>264.9699999999942</v>
@@ -3656,7 +3656,7 @@
         <v>330.7</v>
       </c>
       <c r="K67" t="n">
-        <v>2.649999999999977</v>
+        <v>2.65</v>
       </c>
       <c r="L67" t="n">
         <v>336.8799999999978</v>
@@ -3800,7 +3800,7 @@
         <v>346.75</v>
       </c>
       <c r="K70" t="n">
-        <v>3.699999999999989</v>
+        <v>3.7</v>
       </c>
       <c r="L70" t="n">
         <v>353.2599999999898</v>
@@ -4376,7 +4376,7 @@
         <v>411.15</v>
       </c>
       <c r="K82" t="n">
-        <v>9.649999999999977</v>
+        <v>9.65</v>
       </c>
       <c r="L82" t="n">
         <v>417.3299999999869</v>
@@ -5192,7 +5192,7 @@
         <v>499.95</v>
       </c>
       <c r="K99" t="n">
-        <v>10.34999999999997</v>
+        <v>10.35</v>
       </c>
       <c r="L99" t="n">
         <v>506.1299999999913</v>
